--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:44</t>
+    <t xml:space="preserve">2026-09-10 00:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:52</t>
+    <t xml:space="preserve">2026-09-18 11:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:01</t>
+    <t xml:space="preserve">2026-09-23 14:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:22</t>
+    <t xml:space="preserve">2026-10-02 15:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Santa Juana</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:12</t>
+    <t xml:space="preserve">2026-10-04 10:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:06</t>
+    <t xml:space="preserve">2026-10-05 14:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
